--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/TEXAS_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/TEXAS_2023.xlsx
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C236">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C284">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C438">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C448">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C594">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C953">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C955">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C956">
@@ -31632,7 +31632,7 @@
       </c>
       <c r="B1738" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1738">
